--- a/data/data_analysis/carbon_costs.xlsx
+++ b/data/data_analysis/carbon_costs.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE27A49C-D6BD-492C-9359-11FD55E88877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2AE77E1-89B2-426E-BE5B-9E84213B9597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{402A6D60-5D67-40F0-A8D8-2C5C69F3BFA7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{402A6D60-5D67-40F0-A8D8-2C5C69F3BFA7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Carbon Price" sheetId="1" r:id="rId1"/>
+    <sheet name="Total_Cost_Carbon" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="43">
   <si>
     <t>High Baseline</t>
   </si>
@@ -133,13 +134,83 @@
   <si>
     <t>s2</t>
   </si>
+  <si>
+    <t>Excess</t>
+  </si>
+  <si>
+    <t>excess</t>
+  </si>
+  <si>
+    <t>CO3</t>
+  </si>
+  <si>
+    <t>CDR</t>
+  </si>
+  <si>
+    <t>Million 2025USD</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <r>
+      <t>CO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tax</t>
+    </r>
+  </si>
+  <si>
+    <t>Innovation</t>
+  </si>
+  <si>
+    <t>Economic</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -167,8 +238,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -266,7 +340,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$2</c:f>
+              <c:f>'Carbon Price'!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -306,11 +380,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$J$1</c15:sqref>
+                    <c15:sqref>'Carbon Price'!$B$1:$J$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$1:$J$1</c:f>
+              <c:f>'Carbon Price'!$F$1:$J$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -337,11 +411,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$2:$J$2</c15:sqref>
+                    <c15:sqref>'Carbon Price'!$B$2:$J$2</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$2:$J$2</c:f>
+              <c:f>'Carbon Price'!$F$2:$J$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -375,7 +449,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$3</c:f>
+              <c:f>'Carbon Price'!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -414,11 +488,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$J$1</c15:sqref>
+                    <c15:sqref>'Carbon Price'!$B$1:$J$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$1:$J$1</c:f>
+              <c:f>'Carbon Price'!$F$1:$J$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -445,11 +519,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$3:$J$3</c15:sqref>
+                    <c15:sqref>'Carbon Price'!$B$3:$J$3</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$3:$J$3</c:f>
+              <c:f>'Carbon Price'!$F$3:$J$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -483,7 +557,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$4</c:f>
+              <c:f>'Carbon Price'!$A$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -531,11 +605,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$J$1</c15:sqref>
+                    <c15:sqref>'Carbon Price'!$B$1:$J$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$1:$J$1</c:f>
+              <c:f>'Carbon Price'!$F$1:$J$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -562,11 +636,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$4:$J$4</c15:sqref>
+                    <c15:sqref>'Carbon Price'!$B$4:$J$4</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$4:$J$4</c:f>
+              <c:f>'Carbon Price'!$F$4:$J$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -597,7 +671,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$5</c:f>
+              <c:f>'Carbon Price'!$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -642,11 +716,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$J$1</c15:sqref>
+                    <c15:sqref>'Carbon Price'!$B$1:$J$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$1:$J$1</c:f>
+              <c:f>'Carbon Price'!$F$1:$J$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -673,11 +747,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$5:$J$5</c15:sqref>
+                    <c15:sqref>'Carbon Price'!$B$5:$J$5</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$5:$J$5</c:f>
+              <c:f>'Carbon Price'!$F$5:$J$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -711,7 +785,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$6</c:f>
+              <c:f>'Carbon Price'!$A$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -750,11 +824,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$J$1</c15:sqref>
+                    <c15:sqref>'Carbon Price'!$B$1:$J$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$1:$J$1</c:f>
+              <c:f>'Carbon Price'!$F$1:$J$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -781,11 +855,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$6:$J$6</c15:sqref>
+                    <c15:sqref>'Carbon Price'!$B$6:$J$6</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$6:$J$6</c:f>
+              <c:f>'Carbon Price'!$F$6:$J$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -819,7 +893,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$7</c:f>
+              <c:f>'Carbon Price'!$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -867,11 +941,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$1:$J$1</c15:sqref>
+                    <c15:sqref>'Carbon Price'!$B$1:$J$1</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$1:$J$1</c:f>
+              <c:f>'Carbon Price'!$F$1:$J$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -898,11 +972,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$B$7:$J$7</c15:sqref>
+                    <c15:sqref>'Carbon Price'!$B$7:$J$7</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$7:$J$7</c:f>
+              <c:f>'Carbon Price'!$F$7:$J$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -928,6 +1002,112 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-3DF1-4592-9CCC-4E678AB239E2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Carbon Price'!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Excess</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Carbon Price'!$B$1:$J$1</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Carbon Price'!$F$1:$J$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Carbon Price'!$B$8:$J$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Carbon Price'!$F$8:$J$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="1">
+                  <c:v>337.38600000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>330.88400000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>469.67700000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>321.99099999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D1F1-4057-B6A0-086342806185}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1038,11 +1218,11 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>2025USD/t</a:t>
+                  <a:t>1990USD/t</a:t>
                 </a:r>
                 <a:r>
                   <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> CO2-eq</a:t>
+                  <a:t> C</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -1195,7 +1375,2042 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Path to Net Zero - 2.4 Gt CDR</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CDR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$1:$F$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>23327.098201034099</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>66983.789385885699</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>199805.420259751</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>608065.96042454895</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-07FD-44BB-939C-C65B29A520F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CO2 tax</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$1:$F$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$3:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>919594.25679919799</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>875383.19333602604</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1152936.6086456601</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>845130.26324293995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-07FD-44BB-939C-C65B29A520F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="834530991"/>
+        <c:axId val="834528591"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="834530991"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="834528591"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="834528591"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Million USD</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="834530991"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Path to Net Zero - 1.5 Gt CDR</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CDR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$1:$F$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>19274.709066019201</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>47110.364055907798</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>126416.586136368</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>355668.98749188299</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FAC4-4E63-9617-2321CE2A0A09}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CO2 tax</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$1:$F$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>873204.48572520097</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>871009.31250905897</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1166977.1843831099</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1200736.7084234999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FAC4-4E63-9617-2321CE2A0A09}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="834530991"/>
+        <c:axId val="834528591"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="834530991"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="834528591"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="834528591"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Million USD</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="834530991"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Path to Net Zero - 0.5 Gt CDR</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CDR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$1:$F$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12302.7152715991</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23575.9277337118</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45308.795827680296</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>97441.209537122704</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-934E-4E69-B91F-1BF5E21E7655}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CO2 tax</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$1:$F$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$7:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>878898.35761845496</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>898828.771834846</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1185699.27218844</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1271793.62321767</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-934E-4E69-B91F-1BF5E21E7655}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="834530991"/>
+        <c:axId val="834528591"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="834530991"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="834528591"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="834528591"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Million USD</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="834530991"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Effect</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> of Policies on Carbon Markets in 2050</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CO2 tax</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$C$11:$E$11</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Baseline</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Innovation</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Economic</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$12:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1200736.7084234999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1197074.41202327</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1195154.91085111</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-90EE-40AA-B26B-97AECB81867C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$B$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CDR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$C$11:$E$11</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Baseline</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Innovation</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Economic</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$C$13:$E$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>355668.98749188299</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>303878.406630382</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>347355.151274901</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-90EE-40AA-B26B-97AECB81867C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="979183327"/>
+        <c:axId val="979184287"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="979183327"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="979184287"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="979184287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Million USD</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="979183327"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1738,6 +3953,2026 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1771,6 +6006,159 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>385762</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>80962</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51B04081-674E-51B2-C5AC-BB543DFBA661}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89BBBCB7-7C62-4A6F-8450-17CB22E0C8BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B042F5C2-06F9-46C5-BB23-A67662264456}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>338137</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A7BC7F3-BA66-285D-721D-BBC225A2B841}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2096,7 +6484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{582C602F-D2DA-4FAD-A834-421B3FC08562}">
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
@@ -2613,20 +7001,302 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>337.38600000000002</v>
+      </c>
+      <c r="H8">
+        <v>330.88400000000001</v>
+      </c>
+      <c r="I8">
+        <v>469.67700000000002</v>
+      </c>
+      <c r="J8">
+        <v>321.99099999999999</v>
+      </c>
+      <c r="K8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" t="s">
+        <v>34</v>
+      </c>
+      <c r="U8" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0881DB2A-9C4C-46E9-980E-CFE273FA9402}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1">
+        <v>2035</v>
+      </c>
+      <c r="D1">
+        <v>2040</v>
+      </c>
+      <c r="E1">
+        <v>2045</v>
+      </c>
+      <c r="F1">
+        <v>2050</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2">
+        <v>23327.098201034099</v>
+      </c>
+      <c r="D2">
+        <v>66983.789385885699</v>
+      </c>
+      <c r="E2">
+        <v>199805.420259751</v>
+      </c>
+      <c r="F2">
+        <v>608065.96042454895</v>
+      </c>
+      <c r="G2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3">
+        <v>919594.25679919799</v>
+      </c>
+      <c r="D3">
+        <v>875383.19333602604</v>
+      </c>
+      <c r="E3">
+        <v>1152936.6086456601</v>
+      </c>
+      <c r="F3">
+        <v>845130.26324293995</v>
+      </c>
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4">
+        <v>19274.709066019201</v>
+      </c>
+      <c r="D4">
+        <v>47110.364055907798</v>
+      </c>
+      <c r="E4">
+        <v>126416.586136368</v>
+      </c>
+      <c r="F4">
+        <v>355668.98749188299</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5">
+        <v>873204.48572520097</v>
+      </c>
+      <c r="D5">
+        <v>871009.31250905897</v>
+      </c>
+      <c r="E5">
+        <v>1166977.1843831099</v>
+      </c>
+      <c r="F5">
+        <v>1200736.7084234999</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6">
+        <v>12302.7152715991</v>
+      </c>
+      <c r="D6">
+        <v>23575.9277337118</v>
+      </c>
+      <c r="E6">
+        <v>45308.795827680296</v>
+      </c>
+      <c r="F6">
+        <v>97441.209537122704</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7">
+        <v>878898.35761845496</v>
+      </c>
+      <c r="D7">
+        <v>898828.771834846</v>
+      </c>
+      <c r="E7">
+        <v>1185699.27218844</v>
+      </c>
+      <c r="F7">
+        <v>1271793.62321767</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12">
+        <v>1200736.7084234999</v>
+      </c>
+      <c r="D12">
+        <v>1197074.41202327</v>
+      </c>
+      <c r="E12">
+        <v>1195154.91085111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13">
+        <v>355668.98749188299</v>
+      </c>
+      <c r="D13">
+        <v>303878.406630382</v>
+      </c>
+      <c r="E13">
+        <v>347355.151274901</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data/data_analysis/carbon_costs.xlsx
+++ b/data/data_analysis/carbon_costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2AE77E1-89B2-426E-BE5B-9E84213B9597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38929EB4-CDE0-4D64-B8BD-D5DEDF26DF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{402A6D60-5D67-40F0-A8D8-2C5C69F3BFA7}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="57">
   <si>
     <t>High Baseline</t>
   </si>
@@ -189,6 +189,48 @@
   </si>
   <si>
     <t>Baseline</t>
+  </si>
+  <si>
+    <t>Costs in 2050</t>
+  </si>
+  <si>
+    <t>100 Mt CDR</t>
+  </si>
+  <si>
+    <t>500 Mt CDR</t>
+  </si>
+  <si>
+    <t>1500 Mt CDR</t>
+  </si>
+  <si>
+    <t>2400 Mt CDR</t>
+  </si>
+  <si>
+    <t>4000 Mt CDR</t>
+  </si>
+  <si>
+    <t>Effects of CDR Policy in 2050</t>
+  </si>
+  <si>
+    <t>500 Mt Baseline</t>
+  </si>
+  <si>
+    <t>500 Mt Procurement</t>
+  </si>
+  <si>
+    <t>500 Mt Tax Credit</t>
+  </si>
+  <si>
+    <t>500 Mt Innovation Policy</t>
+  </si>
+  <si>
+    <t>Positive CO2 emissions</t>
+  </si>
+  <si>
+    <t>Positive C emissions</t>
+  </si>
+  <si>
+    <t>Marginal Effectiveness</t>
   </si>
 </sst>
 </file>
@@ -3250,6 +3292,1490 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Cost of Achieving Net Zero 2050 in Various Scenarios</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14532850060409117"/>
+          <c:y val="0.16429652554177632"/>
+          <c:w val="0.82557097029537962"/>
+          <c:h val="0.73203308979814574"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$R$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CDR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$S$3:$W$3</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100 Mt CDR</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500 Mt CDR</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1500 Mt CDR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2400 Mt CDR</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4000 Mt CDR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$S$4:$W$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>16.786343343126799</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>97.441209537122702</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>355.668987491883</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>608.06596042454896</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>947.56924633539904</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-37C6-4463-8E28-0E2438CE4F12}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$R$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CO2 tax</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$S$3:$W$3</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100 Mt CDR</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500 Mt CDR</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1500 Mt CDR</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2400 Mt CDR</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4000 Mt CDR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$S$5:$W$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1292.5256363451399</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1271.7936232176701</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1200.7367084235</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>845.13026324293992</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-37C6-4463-8E28-0E2438CE4F12}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="998777216"/>
+        <c:axId val="998791616"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="998777216"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="998791616"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="998791616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" b="1"/>
+                  <a:t>Billion  USD/yr</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.1164021164021163E-2"/>
+              <c:y val="0.37020792913699702"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="998777216"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.7173226263383744"/>
+          <c:y val="0.16462306960242526"/>
+          <c:w val="0.24251156105486815"/>
+          <c:h val="8.7293538104897136E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Cost of Achieving Net Zero 2050 by Policy Type</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14532850060409117"/>
+          <c:y val="0.16429652554177632"/>
+          <c:w val="0.83615298087739021"/>
+          <c:h val="0.69474161098011766"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$R$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CO2 tax</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$S$8:$V$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>500 Mt Baseline</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500 Mt Procurement</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500 Mt Tax Credit</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500 Mt Innovation Policy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$S$9:$V$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1271.7936232176701</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1278.2202182165702</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1265.46770389566</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1261.2151652570799</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DAF8-4736-82C8-0D3F102381A2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$R$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CDR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$S$8:$V$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>500 Mt Baseline</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500 Mt Procurement</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500 Mt Tax Credit</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500 Mt Innovation Policy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$S$10:$V$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>97.441209537122702</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>97.8415030595731</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>95.558861633785511</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83.465526403645498</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DAF8-4736-82C8-0D3F102381A2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="998777216"/>
+        <c:axId val="998791616"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="998777216"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="998791616"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="998791616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" b="1"/>
+                  <a:t>Billion USD/yr</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.1164021164021163E-2"/>
+              <c:y val="0.37020792913699702"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="998777216"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.7173226263383744"/>
+          <c:y val="0.16462306960242526"/>
+          <c:w val="0.24251156105486815"/>
+          <c:h val="8.7293538104897136E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Moral Hazard of Increasing CDR</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12513648293963256"/>
+          <c:y val="8.305736396855061E-2"/>
+          <c:w val="0.83286351706036732"/>
+          <c:h val="0.82245485258413076"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$Z$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Positive CO2 emissions</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$AA$3:$AE$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$AA$4:$AE$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3277.6882923332319</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3286.8508796772803</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3462.8793427374962</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3865.0223008479497</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4643.0507990947308</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-62FF-4D81-A351-67A8B52251F8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1043522208"/>
+        <c:axId val="1043512608"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1043522208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Mt CDR/yr</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1043512608"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1043512608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Mt</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> CO2 Emissions/yr</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1043522208"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3450,6 +4976,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -5954,6 +7600,1532 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -6164,6 +9336,116 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7858888-3724-6FB2-F95F-574FA0203F1D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>176213</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4767A67-470B-4588-B4F4-F91D239153DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>109535</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>109535</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9B2AFFF-92F9-99AB-0948-53C3F333BF02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7094,10 +10376,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0881DB2A-9C4C-46E9-980E-CFE273FA9402}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -7120,7 +10402,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -7142,8 +10424,29 @@
       <c r="G2" t="s">
         <v>36</v>
       </c>
+      <c r="S2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z2">
+        <v>2050</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
         <v>39</v>
@@ -7163,8 +10466,41 @@
       <c r="G3" t="s">
         <v>36</v>
       </c>
+      <c r="S3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" t="s">
+        <v>46</v>
+      </c>
+      <c r="V3" t="s">
+        <v>47</v>
+      </c>
+      <c r="W3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA3">
+        <v>100</v>
+      </c>
+      <c r="AB3">
+        <v>500</v>
+      </c>
+      <c r="AC3">
+        <v>1500</v>
+      </c>
+      <c r="AD3">
+        <v>2400</v>
+      </c>
+      <c r="AE3">
+        <v>4000</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -7186,8 +10522,49 @@
       <c r="G4" t="s">
         <v>36</v>
       </c>
+      <c r="R4" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4">
+        <v>16.786343343126799</v>
+      </c>
+      <c r="T4">
+        <v>97.441209537122702</v>
+      </c>
+      <c r="U4">
+        <v>355.668987491883</v>
+      </c>
+      <c r="V4">
+        <v>608.06596042454896</v>
+      </c>
+      <c r="W4">
+        <v>947.56924633539904</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" ref="AA4:AD4" si="0">AA5*44/12</f>
+        <v>3277.6882923332319</v>
+      </c>
+      <c r="AB4">
+        <f t="shared" si="0"/>
+        <v>3286.8508796772803</v>
+      </c>
+      <c r="AC4">
+        <f t="shared" si="0"/>
+        <v>3462.8793427374962</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" si="0"/>
+        <v>3865.0223008479497</v>
+      </c>
+      <c r="AE4">
+        <f>AE5*44/12</f>
+        <v>4643.0507990947308</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
         <v>39</v>
@@ -7207,8 +10584,44 @@
       <c r="G5" t="s">
         <v>36</v>
       </c>
+      <c r="R5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S5">
+        <v>1292.5256363451399</v>
+      </c>
+      <c r="T5">
+        <v>1271.7936232176701</v>
+      </c>
+      <c r="U5">
+        <v>1200.7367084235</v>
+      </c>
+      <c r="V5">
+        <v>845.13026324293992</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA5">
+        <v>893.91498881815403</v>
+      </c>
+      <c r="AB5">
+        <v>896.41387627562199</v>
+      </c>
+      <c r="AC5">
+        <v>944.42163892840802</v>
+      </c>
+      <c r="AD5">
+        <v>1054.0969911403499</v>
+      </c>
+      <c r="AE5">
+        <v>1266.2865815712901</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -7230,8 +10643,27 @@
       <c r="G6" t="s">
         <v>36</v>
       </c>
+      <c r="Z6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB6">
+        <f>(AB4-AA4)/(AB3-AA3)</f>
+        <v>2.2906468360121154E-2</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" ref="AC6:AE6" si="1">(AC4-AB4)/(AC3-AB3)</f>
+        <v>0.17602846306021594</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="1"/>
+        <v>0.446825509011615</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" si="1"/>
+        <v>0.48626781140423814</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
         <v>39</v>
@@ -7251,8 +10683,59 @@
       <c r="G7" t="s">
         <v>36</v>
       </c>
+      <c r="S7" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="S8" t="s">
+        <v>50</v>
+      </c>
+      <c r="T8" t="s">
+        <v>51</v>
+      </c>
+      <c r="U8" t="s">
+        <v>52</v>
+      </c>
+      <c r="V8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" ht="18" x14ac:dyDescent="0.35">
+      <c r="R9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S9">
+        <v>1271.7936232176701</v>
+      </c>
+      <c r="T9">
+        <v>1278.2202182165702</v>
+      </c>
+      <c r="U9">
+        <v>1265.46770389566</v>
+      </c>
+      <c r="V9">
+        <v>1261.2151652570799</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="R10" t="s">
+        <v>35</v>
+      </c>
+      <c r="S10">
+        <v>97.441209537122702</v>
+      </c>
+      <c r="T10">
+        <v>97.8415030595731</v>
+      </c>
+      <c r="U10">
+        <v>95.558861633785511</v>
+      </c>
+      <c r="V10">
+        <v>83.465526403645498</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>42</v>
       </c>
@@ -7263,7 +10746,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" ht="18" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>39</v>
       </c>
@@ -7277,7 +10760,7 @@
         <v>1195154.91085111</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>35</v>
       </c>

--- a/data/data_analysis/carbon_costs.xlsx
+++ b/data/data_analysis/carbon_costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9630CC95-41D0-4E8F-B1A7-87BFFEC1971E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25491D4-C3E1-49EA-AC4B-401F88D58DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{402A6D60-5D67-40F0-A8D8-2C5C69F3BFA7}"/>
   </bookViews>
@@ -17,15 +17,9 @@
     <sheet name="Total_Cost_Carbon" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Total_Cost_Carbon!$A$10</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Total_Cost_Carbon!$A$9</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Total_Cost_Carbon!$B$9:$X$9</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Total_Cost_Carbon!$B$9:$Y$9</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Total_Cost_Carbon!$C$9:$X$9</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Total_Cost_Carbon!$C$9:$Y$9</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Total_Cost_Carbon!$A$9</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Total_Cost_Carbon!$B$9:$Y$9</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Total_Cost_Carbon!$C$9:$Y$9</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Total_Cost_Carbon!$A$11</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Total_Cost_Carbon!$A$12</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Total_Cost_Carbon!$C$11:$Y$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="75">
   <si>
     <t>High Baseline</t>
   </si>
@@ -288,12 +282,21 @@
   <si>
     <t>% Reduction in CDR prices to make financial sense</t>
   </si>
+  <si>
+    <t>CDR Market</t>
+  </si>
+  <si>
+    <t>C Tax Revenue</t>
+  </si>
+  <si>
+    <t>Deadweight Loss</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,6 +325,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -344,9 +355,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2068,15 +2080,206 @@
         <c:grouping val="stacked"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Total_Cost_Carbon!$A$7</c:f>
+              <c:f>Total_Cost_Carbon!$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>CO2 tax</c:v>
+                  <c:v>Deadweight Loss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>nzn</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>low</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>innovation-DACSHubs-low</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>innovation-maintain - low</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>innovation-rhodium6B-low</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>innovation-rhodium18b-low</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>innovation-triple-low</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>procurement-3B-low</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>procurement-rhodium-low</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>procurement-scaling-low</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>itc-low</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>itc-noBECCS - low</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>high</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>innovation-DACSHubs-high</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>innovation-maintain - high</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>innovation-rhodium6B-high</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>innovation-rhodium18b-high</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>innovation-triple-high</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>procurement-3B-high</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>procurement-rhodium-high</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>procurement-scaling-high</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>itc-high</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>excess</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4gt</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Total_Cost_Carbon!$B$9:$Y$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>0.80540653315664501</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.76559265041325797</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.75698165001094508</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.76091263338566595</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.76036516565217604</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.75848304958090806</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.76069234447099809</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.76095363317406706</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.66886775892514594</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.76093135692297798</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.76091465243740908</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.76094737747709895</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.546578194077596</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.53980462528722506</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.53783980929351904</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.53009090975417106</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.53695648322714506</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.54328262985981701</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.44039384256177905</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.54253783512312803</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.543356259561663</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.25289689749009103</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-60CB-48ED-BB1E-978F7C867961}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Total_Cost_Carbon!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>C Tax Revenue</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2173,72 +2376,78 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Total_Cost_Carbon!$B$7:$Y$7</c:f>
+              <c:f>Total_Cost_Carbon!$B$8:$Y$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>1.27860438742933</c:v>
+                  <c:v>1.2661769460771801E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2629693925521099</c:v>
+                  <c:v>6.3520126462192295E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.2313929938736296E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2569927519422499</c:v>
+                  <c:v>6.4584048976029401E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.2572171142989801</c:v>
+                  <c:v>6.4726280576981696E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.25691714204483</c:v>
+                  <c:v>6.4831455393355497E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.2567435927077599</c:v>
+                  <c:v>6.3802130694090797E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.25816516656799</c:v>
+                  <c:v>6.6309095375206101E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.23577853344143</c:v>
+                  <c:v>0.19934397205518201</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.25811115831135</c:v>
+                  <c:v>6.6274958472520504E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.25811297887675</c:v>
+                  <c:v>6.6288695092441993E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.2581495617949101</c:v>
+                  <c:v>6.6310365425589102E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.18952237741678</c:v>
+                  <c:v>0.34417585007785201</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.1812324612886902</c:v>
+                  <c:v>0.34849103426654698</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.1807415073891798</c:v>
+                  <c:v>0.350341017696847</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.1772908024397299</c:v>
+                  <c:v>0.35853756413854504</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.1797489205829101</c:v>
+                  <c:v>0.35125332771964596</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.1838738617750999</c:v>
+                  <c:v>0.34543296099800597</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.1378770598829702</c:v>
+                  <c:v>0.45596263167832402</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.18285992639822</c:v>
+                  <c:v>0.344379196492753</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.1838484778690002</c:v>
+                  <c:v>0.34531942562496903</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.85628120400736396</c:v>
+                  <c:v>0.42456509040301799</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -2248,27 +2457,27 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CFC2-407A-8AA6-2C044006A0F6}"/>
+              <c16:uniqueId val="{00000001-CFC2-407A-8AA6-2C044006A0F6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="0"/>
+          <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Total_Cost_Carbon!$A$6</c:f>
+              <c:f>Total_Cost_Carbon!$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>CDR</c:v>
+                  <c:v>CDR Market</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2358,7 +2567,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Total_Cost_Carbon!$B$6:$Y$6</c:f>
+              <c:f>Total_Cost_Carbon!$B$7:$Y$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
@@ -2368,6 +2577,9 @@
                 <c:pt idx="1">
                   <c:v>8.6435333069538905E-2</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.2018275442912902E-2</c:v>
+                </c:pt>
                 <c:pt idx="3">
                   <c:v>8.0543139220406193E-2</c:v>
                 </c:pt>
@@ -2397,6 +2609,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.31633111004002901</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0.29730050001937802</c:v>
@@ -2433,7 +2648,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-CFC2-407A-8AA6-2C044006A0F6}"/>
+              <c16:uniqueId val="{00000000-CFC2-407A-8AA6-2C044006A0F6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2676,7 +2891,7 @@
           <c:yMode val="edge"/>
           <c:x val="9.7623968225095129E-2"/>
           <c:y val="0.12296574601772681"/>
-          <c:w val="0.22430528921840426"/>
+          <c:w val="0.64187031870603606"/>
           <c:h val="5.0605903604822193E-2"/>
         </c:manualLayout>
       </c:layout>
@@ -2755,10 +2970,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f dir="row">_xlchart.v1.0</cx:f>
+        <cx:f dir="row">_xlchart.v1.1</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.5</cx:f>
+        <cx:f dir="row">_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2796,7 +3011,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{5402BA9F-4984-4EB2-B2F1-7A55FABDC951}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:f>_xlchart.v1.0</cx:f>
               <cx:v>% Reduction in CDR prices to make financial sense</cx:v>
             </cx:txData>
           </cx:tx>
@@ -5067,13 +5282,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>80960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>371475</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>80960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5103,13 +5318,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>508905</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>163285</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5139,13 +5354,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>528636</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>138111</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>419099</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>123824</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -6143,11 +6358,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0881DB2A-9C4C-46E9-980E-CFE273FA9402}">
-  <dimension ref="A1:AH65"/>
+  <dimension ref="A1:AH67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B1" t="s">
@@ -6225,7 +6440,7 @@
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="B2">
         <v>18001.5467729845</v>
@@ -6233,6 +6448,9 @@
       <c r="C2">
         <v>86435.333069538901</v>
       </c>
+      <c r="D2">
+        <v>82018.275442912898</v>
+      </c>
       <c r="E2">
         <v>80543.139220406199</v>
       </c>
@@ -6318,72 +6536,75 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="B3">
-        <v>1278604.38742933</v>
+        <v>12661.7694607718</v>
       </c>
       <c r="C3">
-        <v>1262969.3925521099</v>
+        <v>63520.126462192296</v>
+      </c>
+      <c r="D3">
+        <v>72313.929938736299</v>
       </c>
       <c r="E3">
-        <v>1256992.7519422499</v>
+        <v>64584.0489760294</v>
       </c>
       <c r="F3">
-        <v>1257217.11429898</v>
+        <v>64726.280576981699</v>
       </c>
       <c r="G3">
-        <v>1256917.1420448299</v>
+        <v>64831.4553933555</v>
       </c>
       <c r="H3">
-        <v>1256743.5927077599</v>
+        <v>63802.130694090803</v>
       </c>
       <c r="I3">
-        <v>1258165.1665679901</v>
+        <v>66309.095375206103</v>
       </c>
       <c r="J3">
-        <v>1235778.53344143</v>
+        <v>199343.97205518201</v>
       </c>
       <c r="K3">
-        <v>1258111.15831135</v>
+        <v>66274.958472520506</v>
       </c>
       <c r="L3">
-        <v>1258112.97887675</v>
+        <v>66288.695092441994</v>
       </c>
       <c r="M3">
-        <v>1258149.5617949101</v>
+        <v>66310.365425589102</v>
       </c>
       <c r="N3">
-        <v>1189522.37741678</v>
+        <v>344175.85007785202</v>
       </c>
       <c r="P3">
-        <v>1181232.4612886901</v>
+        <v>348491.03426654701</v>
       </c>
       <c r="Q3">
-        <v>1180741.5073891799</v>
+        <v>350341.01769684698</v>
       </c>
       <c r="R3">
-        <v>1177290.8024397299</v>
+        <v>358537.56413854501</v>
       </c>
       <c r="S3">
-        <v>1179748.9205829101</v>
+        <v>351253.32771964598</v>
       </c>
       <c r="T3">
-        <v>1183873.8617751</v>
+        <v>345432.96099800599</v>
       </c>
       <c r="U3">
-        <v>1137877.0598829701</v>
+        <v>455962.63167832402</v>
       </c>
       <c r="V3">
-        <v>1182859.92639822</v>
+        <v>344379.19649275299</v>
       </c>
       <c r="W3">
-        <v>1183848.4778690001</v>
+        <v>345319.42562496901</v>
       </c>
       <c r="X3">
-        <v>856281.20400736399</v>
+        <v>424565.090403018</v>
       </c>
       <c r="Y3">
         <v>0</v>
@@ -6414,11 +6635,80 @@
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4">
+        <v>805406.53315664502</v>
+      </c>
+      <c r="C4">
+        <v>765592.650413258</v>
+      </c>
+      <c r="D4">
+        <v>756981.65001094504</v>
+      </c>
+      <c r="E4">
+        <v>760912.63338566595</v>
+      </c>
+      <c r="F4">
+        <v>760365.16565217602</v>
+      </c>
+      <c r="G4">
+        <v>758483.04958090803</v>
+      </c>
+      <c r="H4">
+        <v>760692.34447099804</v>
+      </c>
+      <c r="I4">
+        <v>760953.63317406701</v>
+      </c>
+      <c r="J4">
+        <v>668867.75892514596</v>
+      </c>
+      <c r="K4">
+        <v>760931.35692297795</v>
+      </c>
+      <c r="L4">
+        <v>760914.65243740904</v>
+      </c>
+      <c r="M4">
+        <v>760947.37747709895</v>
+      </c>
+      <c r="N4">
+        <v>546578.19407759595</v>
+      </c>
+      <c r="P4">
+        <v>539804.625287225</v>
+      </c>
+      <c r="Q4">
+        <v>537839.80929351901</v>
+      </c>
+      <c r="R4">
+        <v>530090.90975417104</v>
+      </c>
+      <c r="S4">
+        <v>536956.48322714504</v>
+      </c>
+      <c r="T4">
+        <v>543282.62985981698</v>
+      </c>
+      <c r="U4">
+        <v>440393.84256177902</v>
+      </c>
+      <c r="V4">
+        <v>542537.83512312802</v>
+      </c>
+      <c r="W4">
+        <v>543356.25956166303</v>
+      </c>
+      <c r="X4">
+        <v>252896.89749009101</v>
+      </c>
       <c r="AA4" t="s">
         <v>42</v>
       </c>
       <c r="AB4">
-        <f t="shared" ref="AB4:AH4" si="0">AB5*44/12</f>
+        <f t="shared" ref="AB4:AH4" si="0">AB6*44/12</f>
         <v>3277.6882923332319</v>
       </c>
       <c r="AC4">
@@ -6446,440 +6736,572 @@
         <v>4637.7985885067828</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AA6" t="s">
         <v>43</v>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <v>893.91498881815403</v>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <v>896.41387627562199</v>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <v>907.40924890148096</v>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <v>944.42163892840802</v>
       </c>
-      <c r="AF5">
+      <c r="AF6">
         <v>1038.78288029233</v>
       </c>
-      <c r="AG5">
+      <c r="AG6">
         <v>1054.0969911403499</v>
       </c>
-      <c r="AH5">
+      <c r="AH6">
         <v>1264.8541605018499</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" t="str">
-        <f>A2</f>
-        <v>CDR</v>
-      </c>
-      <c r="B6">
-        <f>B2/1000000</f>
-        <v>1.80015467729845E-2</v>
-      </c>
-      <c r="C6">
-        <f t="shared" ref="C6:Y6" si="1">C2/1000000</f>
-        <v>8.6435333069538905E-2</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="1"/>
-        <v>8.0543139220406193E-2</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="1"/>
-        <v>7.9191665210007506E-2</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="1"/>
-        <v>7.1784198481042408E-2</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="1"/>
-        <v>7.7449393544863201E-2</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="1"/>
-        <v>8.5043634601615806E-2</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="1"/>
-        <v>0.18412221682811603</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="1"/>
-        <v>8.5039787194114494E-2</v>
-      </c>
-      <c r="L6">
-        <f t="shared" si="1"/>
-        <v>8.5039599125083798E-2</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="1"/>
-        <v>8.5043120568175312E-2</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="1"/>
-        <v>0.31633111004002901</v>
-      </c>
-      <c r="P6">
-        <f t="shared" si="1"/>
-        <v>0.29730050001937802</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="1"/>
-        <v>0.29394780178260499</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>0.273786617657857</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="1"/>
-        <v>0.28960338611407599</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="1"/>
-        <v>0.30825365680427597</v>
-      </c>
-      <c r="U6">
-        <f t="shared" si="1"/>
-        <v>0.42715683625427098</v>
-      </c>
-      <c r="V6">
-        <f t="shared" si="1"/>
-        <v>0.30811729543225003</v>
-      </c>
-      <c r="W6">
-        <f t="shared" si="1"/>
-        <v>0.30821074006138605</v>
-      </c>
-      <c r="X6">
-        <f t="shared" si="1"/>
-        <v>0.555685658074067</v>
-      </c>
-      <c r="Y6">
-        <f t="shared" si="1"/>
-        <v>0.93580300000000005</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC6">
-        <f>(AC4-AB4)/(AC3-AB3)</f>
-        <v>2.2906468360121154E-2</v>
-      </c>
-      <c r="AD6">
-        <f>(AD4-AC4)/(AD3-AC3)</f>
-        <v>8.5055625094550252E-2</v>
-      </c>
-      <c r="AE6">
-        <f t="shared" ref="AD6:AH6" si="2">(AE4-AD4)/(AE3-AD3)</f>
-        <v>0.25800778852737472</v>
-      </c>
-      <c r="AF6">
-        <f t="shared" si="2"/>
-        <v>0.58543353356071137</v>
-      </c>
-      <c r="AG6">
-        <f t="shared" si="2"/>
-        <v>0.1817208406992657</v>
-      </c>
-      <c r="AH6">
-        <f t="shared" si="2"/>
-        <v>0.48298517978677069</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <f>A3</f>
-        <v>CO2 tax</v>
+        <f>A2</f>
+        <v>CDR Market</v>
       </c>
       <c r="B7">
-        <f>B3/1000000</f>
-        <v>1.27860438742933</v>
+        <f>B2/1000000</f>
+        <v>1.80015467729845E-2</v>
       </c>
       <c r="C7">
-        <f t="shared" ref="C7:Y7" si="3">C3/1000000</f>
-        <v>1.2629693925521099</v>
+        <f t="shared" ref="C7:Y7" si="1">C2/1000000</f>
+        <v>8.6435333069538905E-2</v>
+      </c>
+      <c r="D7">
+        <f t="shared" ref="D7:Y7" si="2">D2/1000000</f>
+        <v>8.2018275442912902E-2</v>
       </c>
       <c r="E7">
+        <f t="shared" si="2"/>
+        <v>8.0543139220406193E-2</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="2"/>
+        <v>7.9191665210007506E-2</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="2"/>
+        <v>7.1784198481042408E-2</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="2"/>
+        <v>7.7449393544863201E-2</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="2"/>
+        <v>8.5043634601615806E-2</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="2"/>
+        <v>0.18412221682811603</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>8.5039787194114494E-2</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="2"/>
+        <v>8.5039599125083798E-2</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="2"/>
+        <v>8.5043120568175312E-2</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="2"/>
+        <v>0.31633111004002901</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="2"/>
+        <v>0.29730050001937802</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.29394780178260499</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="2"/>
+        <v>0.273786617657857</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>0.28960338611407599</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="2"/>
+        <v>0.30825365680427597</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="2"/>
+        <v>0.42715683625427098</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="2"/>
+        <v>0.30811729543225003</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="2"/>
+        <v>0.30821074006138605</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="2"/>
+        <v>0.555685658074067</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="2"/>
+        <v>0.93580300000000005</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC7">
+        <f>(AC4-AB4)/(AC3-AB3)</f>
+        <v>2.2906468360121154E-2</v>
+      </c>
+      <c r="AD7">
+        <f>(AD4-AC4)/(AD3-AC3)</f>
+        <v>8.5055625094550252E-2</v>
+      </c>
+      <c r="AE7">
+        <f t="shared" ref="AE7:AH7" si="3">(AE4-AD4)/(AE3-AD3)</f>
+        <v>0.25800778852737472</v>
+      </c>
+      <c r="AF7">
         <f t="shared" si="3"/>
-        <v>1.2569927519422499</v>
-      </c>
-      <c r="F7">
+        <v>0.58543353356071137</v>
+      </c>
+      <c r="AG7">
         <f t="shared" si="3"/>
-        <v>1.2572171142989801</v>
-      </c>
-      <c r="G7">
+        <v>0.1817208406992657</v>
+      </c>
+      <c r="AH7">
         <f t="shared" si="3"/>
-        <v>1.25691714204483</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="3"/>
-        <v>1.2567435927077599</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="3"/>
-        <v>1.25816516656799</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="3"/>
-        <v>1.23577853344143</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="3"/>
-        <v>1.25811115831135</v>
-      </c>
-      <c r="L7">
-        <f t="shared" si="3"/>
-        <v>1.25811297887675</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="3"/>
-        <v>1.2581495617949101</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="3"/>
-        <v>1.18952237741678</v>
-      </c>
-      <c r="P7">
-        <f t="shared" si="3"/>
-        <v>1.1812324612886902</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="3"/>
-        <v>1.1807415073891798</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="3"/>
-        <v>1.1772908024397299</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="3"/>
-        <v>1.1797489205829101</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="3"/>
-        <v>1.1838738617750999</v>
-      </c>
-      <c r="U7">
-        <f t="shared" si="3"/>
-        <v>1.1378770598829702</v>
-      </c>
-      <c r="V7">
-        <f t="shared" si="3"/>
-        <v>1.18285992639822</v>
-      </c>
-      <c r="W7">
-        <f t="shared" si="3"/>
-        <v>1.1838484778690002</v>
-      </c>
-      <c r="X7">
-        <f t="shared" si="3"/>
-        <v>0.85628120400736396</v>
-      </c>
-      <c r="Y7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.48298517978677069</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>70</v>
+      <c r="A8" t="str">
+        <f>A3</f>
+        <v>C Tax Revenue</v>
       </c>
       <c r="B8">
-        <f>SUM(B6:B7)</f>
-        <v>1.2966059342023146</v>
+        <f>B3/1000000</f>
+        <v>1.2661769460771801E-2</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:Y8" si="4">SUM(C6:C7)</f>
-        <v>1.3494047256216488</v>
+        <f t="shared" ref="C8:Y8" si="4">C3/1000000</f>
+        <v>6.3520126462192295E-2</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ref="D8:Y8" si="5">D3/1000000</f>
+        <v>7.2313929938736296E-2</v>
       </c>
       <c r="E8">
-        <f t="shared" si="4"/>
-        <v>1.337535891162656</v>
+        <f t="shared" si="5"/>
+        <v>6.4584048976029401E-2</v>
       </c>
       <c r="F8">
-        <f t="shared" si="4"/>
-        <v>1.3364087795089876</v>
+        <f t="shared" si="5"/>
+        <v>6.4726280576981696E-2</v>
       </c>
       <c r="G8">
-        <f t="shared" si="4"/>
-        <v>1.3287013405258723</v>
+        <f t="shared" si="5"/>
+        <v>6.4831455393355497E-2</v>
       </c>
       <c r="H8">
-        <f t="shared" si="4"/>
-        <v>1.3341929862526232</v>
+        <f t="shared" si="5"/>
+        <v>6.3802130694090797E-2</v>
       </c>
       <c r="I8">
-        <f t="shared" si="4"/>
-        <v>1.3432088011696059</v>
+        <f t="shared" si="5"/>
+        <v>6.6309095375206101E-2</v>
       </c>
       <c r="J8">
-        <f t="shared" si="4"/>
-        <v>1.419900750269546</v>
+        <f t="shared" si="5"/>
+        <v>0.19934397205518201</v>
       </c>
       <c r="K8">
-        <f t="shared" si="4"/>
-        <v>1.3431509455054644</v>
+        <f t="shared" si="5"/>
+        <v>6.6274958472520504E-2</v>
       </c>
       <c r="L8">
-        <f t="shared" si="4"/>
-        <v>1.3431525780018339</v>
+        <f t="shared" si="5"/>
+        <v>6.6288695092441993E-2</v>
       </c>
       <c r="M8">
-        <f t="shared" si="4"/>
-        <v>1.3431926823630853</v>
+        <f t="shared" si="5"/>
+        <v>6.6310365425589102E-2</v>
       </c>
       <c r="N8">
-        <f t="shared" si="4"/>
-        <v>1.505853487456809</v>
+        <f t="shared" si="5"/>
+        <v>0.34417585007785201</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="P8">
-        <f t="shared" si="4"/>
-        <v>1.4785329613080682</v>
+        <f t="shared" si="5"/>
+        <v>0.34849103426654698</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="4"/>
-        <v>1.4746893091717848</v>
+        <f t="shared" si="5"/>
+        <v>0.350341017696847</v>
       </c>
       <c r="R8">
-        <f t="shared" si="4"/>
-        <v>1.4510774200975869</v>
+        <f t="shared" si="5"/>
+        <v>0.35853756413854504</v>
       </c>
       <c r="S8">
-        <f t="shared" si="4"/>
-        <v>1.4693523066969862</v>
+        <f t="shared" si="5"/>
+        <v>0.35125332771964596</v>
       </c>
       <c r="T8">
-        <f t="shared" si="4"/>
-        <v>1.4921275185793759</v>
+        <f t="shared" si="5"/>
+        <v>0.34543296099800597</v>
       </c>
       <c r="U8">
-        <f t="shared" si="4"/>
-        <v>1.5650338961372412</v>
+        <f t="shared" si="5"/>
+        <v>0.45596263167832402</v>
       </c>
       <c r="V8">
-        <f t="shared" si="4"/>
-        <v>1.49097722183047</v>
+        <f t="shared" si="5"/>
+        <v>0.344379196492753</v>
       </c>
       <c r="W8">
-        <f t="shared" si="4"/>
-        <v>1.4920592179303862</v>
+        <f t="shared" si="5"/>
+        <v>0.34531942562496903</v>
       </c>
       <c r="X8">
-        <f t="shared" si="4"/>
-        <v>1.411966862081431</v>
+        <f t="shared" si="5"/>
+        <v>0.42456509040301799</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="4"/>
-        <v>0.93580300000000005</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" t="str">
+        <f>A4</f>
+        <v>Deadweight Loss</v>
+      </c>
+      <c r="B9">
+        <f>B4/1000000</f>
+        <v>0.80540653315664501</v>
+      </c>
+      <c r="C9">
+        <f t="shared" ref="C9:Y9" si="6">C4/1000000</f>
+        <v>0.76559265041325797</v>
+      </c>
+      <c r="D9">
+        <f t="shared" ref="D9:Y9" si="7">D4/1000000</f>
+        <v>0.75698165001094508</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="7"/>
+        <v>0.76091263338566595</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="7"/>
+        <v>0.76036516565217604</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="7"/>
+        <v>0.75848304958090806</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="7"/>
+        <v>0.76069234447099809</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="7"/>
+        <v>0.76095363317406706</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="7"/>
+        <v>0.66886775892514594</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="7"/>
+        <v>0.76093135692297798</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="7"/>
+        <v>0.76091465243740908</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="7"/>
+        <v>0.76094737747709895</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="7"/>
+        <v>0.546578194077596</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="7"/>
+        <v>0.53980462528722506</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="7"/>
+        <v>0.53783980929351904</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="7"/>
+        <v>0.53009090975417106</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="7"/>
+        <v>0.53695648322714506</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="7"/>
+        <v>0.54328262985981701</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="7"/>
+        <v>0.44039384256177905</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="7"/>
+        <v>0.54253783512312803</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="7"/>
+        <v>0.543356259561663</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="7"/>
+        <v>0.25289689749009103</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10">
+        <f>SUM(B7:B9)</f>
+        <v>0.8360698493904013</v>
+      </c>
+      <c r="C10">
+        <f t="shared" ref="C10:Y10" si="8">SUM(C7:C9)</f>
+        <v>0.91554810994498914</v>
+      </c>
+      <c r="D10">
+        <f t="shared" ref="D10" si="9">SUM(D7:D9)</f>
+        <v>0.91131385539259435</v>
+      </c>
+      <c r="E10">
+        <f t="shared" ref="E10" si="10">SUM(E7:E9)</f>
+        <v>0.9060398215821015</v>
+      </c>
+      <c r="F10">
+        <f t="shared" ref="F10" si="11">SUM(F7:F9)</f>
+        <v>0.90428311143916518</v>
+      </c>
+      <c r="G10">
+        <f t="shared" ref="G10" si="12">SUM(G7:G9)</f>
+        <v>0.89509870345530596</v>
+      </c>
+      <c r="H10">
+        <f t="shared" ref="H10" si="13">SUM(H7:H9)</f>
+        <v>0.90194386870995213</v>
+      </c>
+      <c r="I10">
+        <f t="shared" ref="I10" si="14">SUM(I7:I9)</f>
+        <v>0.91230636315088898</v>
+      </c>
+      <c r="J10">
+        <f t="shared" ref="J10" si="15">SUM(J7:J9)</f>
+        <v>1.0523339478084439</v>
+      </c>
+      <c r="K10">
+        <f t="shared" ref="K10" si="16">SUM(K7:K9)</f>
+        <v>0.91224610258961292</v>
+      </c>
+      <c r="L10">
+        <f t="shared" ref="L10" si="17">SUM(L7:L9)</f>
+        <v>0.91224294665493488</v>
+      </c>
+      <c r="M10">
+        <f t="shared" ref="M10" si="18">SUM(M7:M9)</f>
+        <v>0.91230086347086337</v>
+      </c>
+      <c r="N10">
+        <f t="shared" ref="N10" si="19">SUM(N7:N9)</f>
+        <v>1.207085154195477</v>
+      </c>
+      <c r="O10">
+        <f t="shared" ref="O10" si="20">SUM(O7:O9)</f>
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <f t="shared" ref="P10" si="21">SUM(P7:P9)</f>
+        <v>1.1855961595731501</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" ref="Q10" si="22">SUM(Q7:Q9)</f>
+        <v>1.1821286287729711</v>
+      </c>
+      <c r="R10">
+        <f t="shared" ref="R10" si="23">SUM(R7:R9)</f>
+        <v>1.1624150915505731</v>
+      </c>
+      <c r="S10">
+        <f t="shared" ref="S10" si="24">SUM(S7:S9)</f>
+        <v>1.1778131970608672</v>
+      </c>
+      <c r="T10">
+        <f t="shared" ref="T10" si="25">SUM(T7:T9)</f>
+        <v>1.196969247662099</v>
+      </c>
+      <c r="U10">
+        <f t="shared" ref="U10" si="26">SUM(U7:U9)</f>
+        <v>1.3235133104943739</v>
+      </c>
+      <c r="V10">
+        <f t="shared" ref="V10" si="27">SUM(V7:V9)</f>
+        <v>1.195034327048131</v>
+      </c>
+      <c r="W10">
+        <f t="shared" ref="W10" si="28">SUM(W7:W9)</f>
+        <v>1.196886425248018</v>
+      </c>
+      <c r="X10">
+        <f t="shared" ref="X10" si="29">SUM(X7:X9)</f>
+        <v>1.233147645967176</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" ref="Y10" si="30">SUM(Y7:Y9)</f>
+        <v>0.93580300000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="1">
-        <f>(B8-$B$8)/B6</f>
+      <c r="B11" s="1">
+        <f>(B10-$B$10)/B7</f>
         <v>0</v>
       </c>
-      <c r="C9" s="1">
-        <f t="shared" ref="C9:Y9" si="5">(C8-$B$8)/C6</f>
-        <v>0.61084731838606487</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.50817434428942032</v>
-      </c>
-      <c r="F9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.50261407183597251</v>
-      </c>
-      <c r="G9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.44710962861880804</v>
-      </c>
-      <c r="H9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.48531112162338541</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.54798771460793005</v>
-      </c>
-      <c r="J9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.66963573538945065</v>
-      </c>
-      <c r="K9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.54733217049220384</v>
-      </c>
-      <c r="L9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.54735257783911107</v>
-      </c>
-      <c r="M9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.54780148999147027</v>
-      </c>
-      <c r="N9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.66148268890788486</v>
-      </c>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.61192977170874452</v>
-      </c>
-      <c r="Q9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.60583332785449873</v>
-      </c>
-      <c r="R9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.56420393084482567</v>
-      </c>
-      <c r="S9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.59649293059932007</v>
-      </c>
-      <c r="T9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.63428796402310528</v>
-      </c>
-      <c r="U9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.62840610088033599</v>
-      </c>
-      <c r="V9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.63083536857441502</v>
-      </c>
-      <c r="W9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.63415468159592148</v>
-      </c>
-      <c r="X9" s="1">
-        <f t="shared" si="5"/>
-        <v>0.20760105322664266</v>
-      </c>
-      <c r="Y9" s="1">
-        <f t="shared" si="5"/>
-        <v>-0.3855543679623965</v>
+      <c r="C11" s="1">
+        <f t="shared" ref="C11:Y11" si="31">(C10-$B$10)/C7</f>
+        <v>0.91951124305434262</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" ref="D11:Y11" si="32">(D10-$B$10)/D7</f>
+        <v>0.91740536600973843</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="32"/>
+        <v>0.86872665839640872</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" si="32"/>
+        <v>0.86136920934633565</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="32"/>
+        <v>0.82230985807403945</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="32"/>
+        <v>0.8505427390001804</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" si="32"/>
+        <v>0.89643997599132719</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="32"/>
+        <v>1.1745681870642046</v>
+      </c>
+      <c r="K11" s="1">
+        <f t="shared" si="32"/>
+        <v>0.89577191703607284</v>
+      </c>
+      <c r="L11" s="1">
+        <f t="shared" si="32"/>
+        <v>0.89573678672322321</v>
+      </c>
+      <c r="M11" s="1">
+        <f t="shared" si="32"/>
+        <v>0.89638072510934064</v>
+      </c>
+      <c r="N11" s="1">
+        <f t="shared" si="32"/>
+        <v>1.1728701130853898</v>
+      </c>
+      <c r="O11" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P11" s="1">
+        <f t="shared" si="32"/>
+        <v>1.1756667417645337</v>
+      </c>
+      <c r="Q11" s="1">
+        <f t="shared" si="32"/>
+        <v>1.1772796982455562</v>
+      </c>
+      <c r="R11" s="1">
+        <f t="shared" si="32"/>
+        <v>1.1919692969361846</v>
+      </c>
+      <c r="S11" s="1">
+        <f t="shared" si="32"/>
+        <v>1.180039198629576</v>
+      </c>
+      <c r="T11" s="1">
+        <f t="shared" si="32"/>
+        <v>1.1707870784509424</v>
+      </c>
+      <c r="U11" s="1">
+        <f t="shared" si="32"/>
+        <v>1.141134636585367</v>
+      </c>
+      <c r="V11" s="1">
+        <f t="shared" si="32"/>
+        <v>1.165025407464217</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" si="32"/>
+        <v>1.1706813843857395</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" si="32"/>
+        <v>0.71457269196580275</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" si="32"/>
+        <v>0.10657494217222936</v>
       </c>
     </row>
-    <row r="65" spans="1:1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+    <row r="67" spans="1:1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>36</v>
       </c>
     </row>

--- a/data/data_analysis/carbon_costs.xlsx
+++ b/data/data_analysis/carbon_costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25491D4-C3E1-49EA-AC4B-401F88D58DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF191F90-DE7D-44A0-9620-C2FE56239DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{402A6D60-5D67-40F0-A8D8-2C5C69F3BFA7}"/>
   </bookViews>
@@ -2229,7 +2229,7 @@
                   <c:v>0.546578194077596</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>0.54098264071816804</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0.53980462528722506</c:v>
@@ -2420,7 +2420,7 @@
                   <c:v>0.34417585007785201</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>0.35092100542190802</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0.34849103426654698</c:v>
@@ -2611,7 +2611,7 @@
                   <c:v>0.31633111004002901</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>0.29268828599462404</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0.29730050001937802</c:v>
@@ -2809,7 +2809,7 @@
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>Trillion USD</a:t>
+                  <a:t>Trillion USD/yr</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -5397,7 +5397,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9672636" y="2652711"/>
+              <a:off x="9672636" y="2995611"/>
               <a:ext cx="2328863" cy="3605213"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6481,6 +6481,9 @@
       <c r="N2">
         <v>316331.11004002899</v>
       </c>
+      <c r="O2">
+        <v>292688.28599462402</v>
+      </c>
       <c r="P2">
         <v>297300.50001937803</v>
       </c>
@@ -6579,6 +6582,9 @@
       <c r="N3">
         <v>344175.85007785202</v>
       </c>
+      <c r="O3">
+        <v>350921.00542190799</v>
+      </c>
       <c r="P3">
         <v>348491.03426654701</v>
       </c>
@@ -6676,6 +6682,9 @@
       </c>
       <c r="N4">
         <v>546578.19407759595</v>
+      </c>
+      <c r="O4">
+        <v>540982.640718168</v>
       </c>
       <c r="P4">
         <v>539804.625287225</v>
@@ -6775,7 +6784,7 @@
         <v>1.80015467729845E-2</v>
       </c>
       <c r="C7">
-        <f t="shared" ref="C7:Y7" si="1">C2/1000000</f>
+        <f t="shared" ref="C7" si="1">C2/1000000</f>
         <v>8.6435333069538905E-2</v>
       </c>
       <c r="D7">
@@ -6824,7 +6833,7 @@
       </c>
       <c r="O7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.29268828599462404</v>
       </c>
       <c r="P7">
         <f t="shared" si="2"/>
@@ -6904,7 +6913,7 @@
         <v>1.2661769460771801E-2</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:Y8" si="4">C3/1000000</f>
+        <f t="shared" ref="C8" si="4">C3/1000000</f>
         <v>6.3520126462192295E-2</v>
       </c>
       <c r="D8">
@@ -6953,7 +6962,7 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.35092100542190802</v>
       </c>
       <c r="P8">
         <f t="shared" si="5"/>
@@ -7006,7 +7015,7 @@
         <v>0.80540653315664501</v>
       </c>
       <c r="C9">
-        <f t="shared" ref="C9:Y9" si="6">C4/1000000</f>
+        <f t="shared" ref="C9" si="6">C4/1000000</f>
         <v>0.76559265041325797</v>
       </c>
       <c r="D9">
@@ -7055,7 +7064,7 @@
       </c>
       <c r="O9">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.54098264071816804</v>
       </c>
       <c r="P9">
         <f t="shared" si="7"/>
@@ -7107,7 +7116,7 @@
         <v>0.8360698493904013</v>
       </c>
       <c r="C10">
-        <f t="shared" ref="C10:Y10" si="8">SUM(C7:C9)</f>
+        <f t="shared" ref="C10" si="8">SUM(C7:C9)</f>
         <v>0.91554810994498914</v>
       </c>
       <c r="D10">
@@ -7156,7 +7165,7 @@
       </c>
       <c r="O10">
         <f t="shared" ref="O10" si="20">SUM(O7:O9)</f>
-        <v>0</v>
+        <v>1.1845919321347003</v>
       </c>
       <c r="P10">
         <f t="shared" ref="P10" si="21">SUM(P7:P9)</f>
@@ -7208,7 +7217,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="1">
-        <f t="shared" ref="C11:Y11" si="31">(C10-$B$10)/C7</f>
+        <f t="shared" ref="C11" si="31">(C10-$B$10)/C7</f>
         <v>0.91951124305434262</v>
       </c>
       <c r="D11" s="1">
@@ -7255,9 +7264,9 @@
         <f t="shared" si="32"/>
         <v>1.1728701130853898</v>
       </c>
-      <c r="O11" s="1" t="e">
+      <c r="O11" s="1">
         <f t="shared" si="32"/>
-        <v>#DIV/0!</v>
+        <v>1.1907619792843382</v>
       </c>
       <c r="P11" s="1">
         <f t="shared" si="32"/>
